--- a/docs/Análisis de Insights y MiniInforme.xlsx
+++ b/docs/Análisis de Insights y MiniInforme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Portfolio\Allegheny-County-Tax-Liens\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6155B09E-10B7-47FA-B66C-56C5B597FAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0BF735-1ED0-435D-8B25-FB09CAD83B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,9 @@
     <definedName name="_xlchart.v2.0" hidden="1">'DashBoards de Insights'!$AA$2</definedName>
     <definedName name="_xlchart.v2.1" hidden="1">'DashBoards de Insights'!$AA$3:$AA$12</definedName>
     <definedName name="_xlchart.v2.2" hidden="1">'DashBoards de Insights'!$Z$3:$Z$12</definedName>
+    <definedName name="_xlchart.v2.5" hidden="1">'DashBoards de Insights'!$AA$2</definedName>
+    <definedName name="_xlchart.v2.6" hidden="1">'DashBoards de Insights'!$AA$3:$AA$12</definedName>
+    <definedName name="_xlchart.v2.7" hidden="1">'DashBoards de Insights'!$Z$3:$Z$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1028,14 +1031,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1089,7 +1092,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>Deuda total por año fiscal</a:t>
             </a:r>
           </a:p>
@@ -2073,6 +2076,39 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES" sz="1600"/>
+              <a:t>Evolución de gravámenes por año</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12449300087489067"/>
+          <c:y val="4.6296296296296294E-3"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2143,7 +2179,17 @@
       </c:spPr>
     </c:backWall>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.6644575678040247E-2"/>
+          <c:y val="0.19095764071157773"/>
+          <c:w val="0.7691371391076115"/>
+          <c:h val="0.7038717556138816"/>
+        </c:manualLayout>
+      </c:layout>
       <c:pie3DChart>
         <c:varyColors val="1"/>
         <c:ser>
@@ -3767,6 +3813,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.88575962379702533"/>
+          <c:y val="0.14763597258675998"/>
+          <c:w val="9.4795931758530183E-2"/>
+          <c:h val="0.78125546806649171"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3838,10 +3894,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v2.2</cx:f>
+        <cx:f>_xlchart.v2.7</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v2.1</cx:f>
+        <cx:f>_xlchart.v2.6</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -3860,7 +3916,7 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="es-ES" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
@@ -3887,7 +3943,7 @@
         <cx:series layoutId="funnel" uniqueId="{C13392F2-811B-48AD-A5EA-F054A5090380}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v2.0</cx:f>
+              <cx:f>_xlchart.v2.5</cx:f>
               <cx:v>transaction_amount</cx:v>
             </cx:txData>
           </cx:tx>
@@ -3953,7 +4009,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:rPr lang="es-ES" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000">
                     <a:lumMod val="65000"/>
@@ -3966,7 +4022,7 @@
               </a:rPr>
               <a:t>Total de deuda por municipio</a:t>
             </a:r>
-            <a:endParaRPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:endParaRPr lang="es-ES" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
@@ -7516,7 +7572,7 @@
       <c r="E39" s="3">
         <v>79</v>
       </c>
-      <c r="G39" s="42" t="s">
+      <c r="G39" s="40" t="s">
         <v>210</v>
       </c>
       <c r="H39" s="38"/>
@@ -7835,25 +7891,25 @@
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="26"/>
-      <c r="W1" s="41" t="s">
+      <c r="W1" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="X1" s="41"/>
+      <c r="X1" s="42"/>
       <c r="Y1" s="27"/>
-      <c r="Z1" s="41" t="s">
+      <c r="Z1" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="AA1" s="41"/>
+      <c r="AA1" s="42"/>
       <c r="AB1" s="27"/>
-      <c r="AC1" s="41" t="s">
+      <c r="AC1" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AG1" s="40" t="s">
+      <c r="AD1" s="42"/>
+      <c r="AE1" s="42"/>
+      <c r="AG1" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="AH1" s="40"/>
+      <c r="AH1" s="41"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="W2" s="30" t="s">
